--- a/Result/profitability/6108.xlsx
+++ b/Result/profitability/6108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08124999999999996</v>
+        <v>-0.19</v>
       </c>
       <c r="N2" t="n">
-        <v>3.465</v>
+        <v>4.4675</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.295</v>
+        <v>0.04250000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>5.24125</v>
+        <v>6.86125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03124999999999992</v>
+        <v>0.18875</v>
       </c>
       <c r="N4" t="n">
-        <v>7.67625</v>
+        <v>8.143750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03375000000000009</v>
+        <v>0.25875</v>
       </c>
       <c r="N5" t="n">
-        <v>9.087499999999999</v>
+        <v>9.422499999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1050000000000001</v>
+        <v>0.29875</v>
       </c>
       <c r="N6" t="n">
-        <v>9.959999999999999</v>
+        <v>10.39625</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3237500000000001</v>
+        <v>0.4950000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>12.30125</v>
+        <v>13.98375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5175000000000001</v>
+        <v>0.8275000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.7</v>
+        <v>17.69</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1408</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1265</v>
+      </c>
+      <c r="E75" t="n">
+        <v>143</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>245</v>
+      </c>
+      <c r="J75" t="n">
+        <v>239</v>
+      </c>
+      <c r="K75" t="n">
+        <v>217</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.05125000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2.59625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.296296296296296</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.749568221070812</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.680000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.359731543624161</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
